--- a/SPEEDY-PWR PINOUT.xlsx
+++ b/SPEEDY-PWR PINOUT.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29917"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EBA8DA5E-F370-456B-8904-ACFDC0A763D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0B6AE2A3-998A-4940-861D-A38DAE586012}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -474,28 +474,10 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -507,6 +489,24 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1297,21 +1297,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="30" customHeight="1">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="27" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="25"/>
-      <c r="C1" s="25"/>
-      <c r="D1" s="26"/>
+      <c r="B1" s="27"/>
+      <c r="C1" s="27"/>
+      <c r="D1" s="28"/>
       <c r="E1" s="19"/>
     </row>
     <row r="2" spans="1:5" ht="30" customHeight="1">
-      <c r="A2" s="27" t="s">
+      <c r="A2" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="27"/>
-      <c r="C2" s="27"/>
-      <c r="D2" s="28"/>
+      <c r="B2" s="29"/>
+      <c r="C2" s="29"/>
+      <c r="D2" s="30"/>
       <c r="E2" s="19"/>
     </row>
     <row r="3" spans="1:5" s="13" customFormat="1" ht="31.5" customHeight="1">
@@ -1327,7 +1327,7 @@
       <c r="D3" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="E3" s="30" t="s">
+      <c r="E3" s="24" t="s">
         <v>6</v>
       </c>
     </row>
@@ -1339,7 +1339,7 @@
         <v>7</v>
       </c>
       <c r="C4" s="17"/>
-      <c r="D4" s="29" t="s">
+      <c r="D4" s="23" t="s">
         <v>8</v>
       </c>
       <c r="E4" s="17"/>
@@ -1355,7 +1355,7 @@
       <c r="D5" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="E5" s="23"/>
+      <c r="E5" s="21"/>
     </row>
     <row r="6" spans="1:5" s="14" customFormat="1" ht="21">
       <c r="A6" s="17">
@@ -1491,12 +1491,12 @@
       <c r="A16" s="16">
         <v>13</v>
       </c>
-      <c r="B16" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="C16" s="17"/>
-      <c r="D16" s="17" t="s">
-        <v>24</v>
+      <c r="B16" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="C16" s="15"/>
+      <c r="D16" s="15" t="s">
+        <v>26</v>
       </c>
       <c r="E16" s="17"/>
     </row>
@@ -1511,19 +1511,19 @@
       <c r="D17" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="E17" s="24"/>
+      <c r="E17" s="22"/>
     </row>
     <row r="18" spans="1:5" ht="23.25">
-      <c r="A18" s="21" t="s">
+      <c r="A18" s="31" t="s">
         <v>29</v>
       </c>
-      <c r="B18" s="22"/>
-      <c r="C18" s="22"/>
-      <c r="D18" s="22"/>
-      <c r="E18" s="31"/>
+      <c r="B18" s="32"/>
+      <c r="C18" s="32"/>
+      <c r="D18" s="32"/>
+      <c r="E18" s="25"/>
     </row>
     <row r="19" spans="1:5" ht="41.25">
-      <c r="A19" s="32" t="s">
+      <c r="A19" s="26" t="s">
         <v>30</v>
       </c>
       <c r="B19" s="11" t="s">
@@ -1612,7 +1612,7 @@
     <hyperlink ref="E23" r:id="rId4" xr:uid="{B438FCE9-8ACD-4E22-975C-176EF7E40CD3}"/>
   </hyperlinks>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" fitToHeight="0" orientation="portrait"/>
+  <pageSetup paperSize="9" fitToHeight="0" orientation="landscape"/>
   <tableParts count="2">
     <tablePart r:id="rId5"/>
     <tablePart r:id="rId6"/>
